--- a/examples/benchmark_results/gmm_discretization_results_test_2025-06-19_4.xlsx
+++ b/examples/benchmark_results/gmm_discretization_results_test_2025-06-19_4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizealwash/PycharmProjects/discretize_distributions_new/examples/benchmark_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE46E05-EE17-8442-83DE-39A5AE992A96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65A0001-24B4-764E-B834-2F33D7680039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>run</t>
   </si>
@@ -67,12 +67,15 @@
   <si>
     <t>nr_locs_old</t>
   </si>
+  <si>
+    <t>Difference in w2 error</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +88,12 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -94,7 +103,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -117,13 +126,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -439,10 +460,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -476,8 +497,11 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -511,8 +535,12 @@
       <c r="K2">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M2">
+        <f>F2-D2</f>
+        <v>0.42435542494058609</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -546,8 +574,12 @@
       <c r="K3">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M3">
+        <f>F3-D3</f>
+        <v>0.13405080437660222</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -581,8 +613,12 @@
       <c r="K4">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M4">
+        <f>F4-D4</f>
+        <v>0.13026480004191399</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -616,8 +652,12 @@
       <c r="K5">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M5">
+        <f>F5-D5</f>
+        <v>0.30873206257820129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -651,8 +691,12 @@
       <c r="K6">
         <v>72</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M6">
+        <f t="shared" ref="M6:M69" si="0">F6-D6</f>
+        <v>0.4917180813848972</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -686,8 +730,12 @@
       <c r="K7">
         <v>26</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>0.37491045296192166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -721,8 +769,12 @@
       <c r="K8">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>0.31316670179367068</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -756,8 +808,12 @@
       <c r="K9">
         <v>56</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>0.29849998354911805</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -791,8 +847,12 @@
       <c r="K10">
         <v>90</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M10">
+        <f t="shared" si="0"/>
+        <v>0.2769192695617676</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -826,8 +886,12 @@
       <c r="K11">
         <v>39</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M11">
+        <f t="shared" si="0"/>
+        <v>0.46854681447148327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -861,8 +925,12 @@
       <c r="K12">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M12">
+        <f t="shared" si="0"/>
+        <v>0.28312369883060456</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -896,8 +964,12 @@
       <c r="K13">
         <v>78</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M13">
+        <f t="shared" si="0"/>
+        <v>9.4335494190454505E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -931,8 +1003,12 @@
       <c r="K14">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M14">
+        <f t="shared" si="0"/>
+        <v>0.51393003910779955</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -966,8 +1042,12 @@
       <c r="K15">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M15">
+        <f t="shared" si="0"/>
+        <v>0.14524785876274116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1001,8 +1081,12 @@
       <c r="K16">
         <v>60</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M16">
+        <f t="shared" si="0"/>
+        <v>0.15120411515235899</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1036,8 +1120,12 @@
       <c r="K17">
         <v>77</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M17">
+        <f t="shared" si="0"/>
+        <v>0.31010179519653325</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1071,8 +1159,12 @@
       <c r="K18">
         <v>53</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M18">
+        <f t="shared" si="0"/>
+        <v>0.18044413626194</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1106,8 +1198,12 @@
       <c r="K19">
         <v>80</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M19">
+        <f t="shared" si="0"/>
+        <v>0.11328341960906985</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1141,8 +1237,12 @@
       <c r="K20">
         <v>51</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M20">
+        <f t="shared" si="0"/>
+        <v>0.15881597697734828</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1176,8 +1276,12 @@
       <c r="K21">
         <v>88</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M21">
+        <f t="shared" si="0"/>
+        <v>6.8193301558495123E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1211,8 +1315,12 @@
       <c r="K22">
         <v>85</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M22">
+        <f t="shared" si="0"/>
+        <v>0.2828422904014587</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1246,8 +1354,12 @@
       <c r="K23">
         <v>82</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M23">
+        <f t="shared" si="0"/>
+        <v>0.42087882310152053</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1281,8 +1393,12 @@
       <c r="K24">
         <v>76</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M24">
+        <f t="shared" si="0"/>
+        <v>0.28509759902954102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1316,8 +1432,12 @@
       <c r="K25">
         <v>80</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M25">
+        <f t="shared" si="0"/>
+        <v>0.28280810415744784</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1351,8 +1471,12 @@
       <c r="K26">
         <v>46</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M26">
+        <f t="shared" si="0"/>
+        <v>0.29868227243423462</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1386,8 +1510,12 @@
       <c r="K27">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M27">
+        <f t="shared" si="0"/>
+        <v>0.3551883578300476</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1421,8 +1549,12 @@
       <c r="K28">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M28">
+        <f t="shared" si="0"/>
+        <v>0.45586127266287801</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1456,8 +1588,12 @@
       <c r="K29">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M29">
+        <f t="shared" si="0"/>
+        <v>0.31424535214900973</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1491,8 +1627,12 @@
       <c r="K30">
         <v>84</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M30">
+        <f t="shared" si="0"/>
+        <v>0.29533287286758425</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1526,8 +1666,12 @@
       <c r="K31">
         <v>72</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M31">
+        <f t="shared" si="0"/>
+        <v>0.16832246184349064</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1561,8 +1705,12 @@
       <c r="K32">
         <v>83</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M32">
+        <f t="shared" si="0"/>
+        <v>0.35135673880577084</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1596,8 +1744,12 @@
       <c r="K33">
         <v>44</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M33">
+        <f t="shared" si="0"/>
+        <v>0.28806410431861873</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1631,8 +1783,12 @@
       <c r="K34">
         <v>63</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M34">
+        <f t="shared" si="0"/>
+        <v>0.22511557713150979</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1666,8 +1822,12 @@
       <c r="K35">
         <v>91</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M35">
+        <f t="shared" si="0"/>
+        <v>0.29541057348251343</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1701,8 +1861,12 @@
       <c r="K36">
         <v>90</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M36">
+        <f t="shared" si="0"/>
+        <v>0.38033551275730132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1736,8 +1900,12 @@
       <c r="K37">
         <v>81</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M37">
+        <f t="shared" si="0"/>
+        <v>0.21003168225288388</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1771,8 +1939,12 @@
       <c r="K38">
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M38">
+        <f t="shared" si="0"/>
+        <v>0.28564978241920469</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1806,8 +1978,12 @@
       <c r="K39">
         <v>58</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M39">
+        <f t="shared" si="0"/>
+        <v>0.31064614653587341</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1841,8 +2017,12 @@
       <c r="K40">
         <v>44</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M40">
+        <f t="shared" si="0"/>
+        <v>0.20432294309139251</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1876,8 +2056,12 @@
       <c r="K41">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M41">
+        <f t="shared" si="0"/>
+        <v>0.30908927321434021</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1911,8 +2095,12 @@
       <c r="K42">
         <v>25</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M42">
+        <f t="shared" si="0"/>
+        <v>0.28592815399169919</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1946,8 +2134,12 @@
       <c r="K43">
         <v>80</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M43">
+        <f t="shared" si="0"/>
+        <v>0.17275756597518921</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1981,8 +2173,12 @@
       <c r="K44">
         <v>86</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M44">
+        <f t="shared" si="0"/>
+        <v>0.28974645733833315</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2016,8 +2212,12 @@
       <c r="K45">
         <v>50</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M45">
+        <f t="shared" si="0"/>
+        <v>0.33463404178619383</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2051,8 +2251,12 @@
       <c r="K46">
         <v>45</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M46">
+        <f t="shared" si="0"/>
+        <v>0.49530906602740288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2086,8 +2290,12 @@
       <c r="K47">
         <v>45</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M47">
+        <f t="shared" si="0"/>
+        <v>0.2796593934297561</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2121,8 +2329,12 @@
       <c r="K48">
         <v>38</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M48">
+        <f t="shared" si="0"/>
+        <v>0.28836967349052428</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2156,8 +2368,12 @@
       <c r="K49">
         <v>88</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M49">
+        <f t="shared" si="0"/>
+        <v>0.28126475214958191</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2191,8 +2407,12 @@
       <c r="K50">
         <v>61</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M50">
+        <f t="shared" si="0"/>
+        <v>0.28490434885025029</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2226,8 +2446,12 @@
       <c r="K51">
         <v>93</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M51">
+        <f t="shared" si="0"/>
+        <v>0.37680193185806282</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2261,8 +2485,12 @@
       <c r="K52">
         <v>25</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M52">
+        <f t="shared" si="0"/>
+        <v>0.39402616322040557</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2296,8 +2524,12 @@
       <c r="K53">
         <v>33</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M53">
+        <f t="shared" si="0"/>
+        <v>0.4059864029288292</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2331,8 +2563,12 @@
       <c r="K54">
         <v>67</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M54">
+        <f t="shared" si="0"/>
+        <v>0.3287437170743942</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2366,8 +2602,12 @@
       <c r="K55">
         <v>64</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M55">
+        <f t="shared" si="0"/>
+        <v>0.12821512222290044</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2401,8 +2641,12 @@
       <c r="K56">
         <v>38</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M56">
+        <f t="shared" si="0"/>
+        <v>0.32510112226009363</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2436,8 +2680,12 @@
       <c r="K57">
         <v>30</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M57">
+        <f t="shared" si="0"/>
+        <v>0.44462646991014482</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2471,8 +2719,12 @@
       <c r="K58">
         <v>62</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M58">
+        <f t="shared" si="0"/>
+        <v>0.36335085332393646</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2506,8 +2758,12 @@
       <c r="K59">
         <v>36</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M59">
+        <f t="shared" si="0"/>
+        <v>0.36754123866558075</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2541,8 +2797,12 @@
       <c r="K60">
         <v>85</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M60">
+        <f t="shared" si="0"/>
+        <v>0.49255508258938785</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2576,8 +2836,12 @@
       <c r="K61">
         <v>56</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M61">
+        <f t="shared" si="0"/>
+        <v>0.47707145735621453</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2611,8 +2875,12 @@
       <c r="K62">
         <v>49</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M62">
+        <f t="shared" si="0"/>
+        <v>0.20317886322736745</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2646,8 +2914,12 @@
       <c r="K63">
         <v>39</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M63">
+        <f t="shared" si="0"/>
+        <v>0.30983812808990474</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2681,8 +2953,12 @@
       <c r="K64">
         <v>40</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M64">
+        <f t="shared" si="0"/>
+        <v>0.3245926320552826</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2716,8 +2992,12 @@
       <c r="K65">
         <v>63</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M65">
+        <f t="shared" si="0"/>
+        <v>7.1432927250862144E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2751,8 +3031,12 @@
       <c r="K66">
         <v>54</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M66">
+        <f t="shared" si="0"/>
+        <v>0.30926350951194759</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2786,8 +3070,12 @@
       <c r="K67">
         <v>93</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M67">
+        <f t="shared" si="0"/>
+        <v>0.2973187327384948</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2821,8 +3109,12 @@
       <c r="K68">
         <v>99</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M68">
+        <f t="shared" si="0"/>
+        <v>0.30827573537826536</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2856,8 +3148,12 @@
       <c r="K69">
         <v>41</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M69">
+        <f t="shared" si="0"/>
+        <v>0.29478496909141538</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2891,8 +3187,12 @@
       <c r="K70">
         <v>41</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M70">
+        <f t="shared" ref="M70:M101" si="1">F70-D70</f>
+        <v>0.31789008975028987</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2926,8 +3226,12 @@
       <c r="K71">
         <v>84</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M71">
+        <f t="shared" si="1"/>
+        <v>7.4115851521492082E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2961,8 +3265,12 @@
       <c r="K72">
         <v>34</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M72">
+        <f t="shared" si="1"/>
+        <v>0.33649864494800563</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2996,8 +3304,12 @@
       <c r="K73">
         <v>38</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M73">
+        <f t="shared" si="1"/>
+        <v>0.37312373816967009</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3031,8 +3343,12 @@
       <c r="K74">
         <v>87</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M74">
+        <f t="shared" si="1"/>
+        <v>0.33506263196468355</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3066,8 +3382,12 @@
       <c r="K75">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M75">
+        <f t="shared" si="1"/>
+        <v>4.9519667029380821E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3101,8 +3421,12 @@
       <c r="K76">
         <v>99</v>
       </c>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M76">
+        <f t="shared" si="1"/>
+        <v>0.35778060257434846</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3136,8 +3460,12 @@
       <c r="K77">
         <v>95</v>
       </c>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M77">
+        <f t="shared" si="1"/>
+        <v>0.36239284873008726</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3171,8 +3499,12 @@
       <c r="K78">
         <v>68</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M78">
+        <f t="shared" si="1"/>
+        <v>0.14737867712974551</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3206,8 +3538,12 @@
       <c r="K79">
         <v>86</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M79">
+        <f t="shared" si="1"/>
+        <v>0.50314789637923241</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -3241,8 +3577,12 @@
       <c r="K80">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M80">
+        <f t="shared" si="1"/>
+        <v>0.29444864392280584</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -3276,8 +3616,12 @@
       <c r="K81">
         <v>37</v>
       </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M81">
+        <f t="shared" si="1"/>
+        <v>0.29834274053573606</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -3311,8 +3655,12 @@
       <c r="K82">
         <v>51</v>
       </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M82">
+        <f t="shared" si="1"/>
+        <v>0.29080004096031187</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -3346,8 +3694,12 @@
       <c r="K83">
         <v>97</v>
       </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M83">
+        <f t="shared" si="1"/>
+        <v>0.29830493330955499</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -3381,8 +3733,12 @@
       <c r="K84">
         <v>30</v>
       </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M84">
+        <f>F84-D84</f>
+        <v>0.35840639770030974</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -3416,8 +3772,12 @@
       <c r="K85">
         <v>55</v>
       </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M85">
+        <f t="shared" si="1"/>
+        <v>0.28566527962684629</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -3451,8 +3811,12 @@
       <c r="K86">
         <v>70</v>
       </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M86">
+        <f t="shared" si="1"/>
+        <v>0.28655227422714236</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -3486,8 +3850,12 @@
       <c r="K87">
         <v>91</v>
       </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M87">
+        <f t="shared" si="1"/>
+        <v>0.28646925091743469</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -3521,8 +3889,12 @@
       <c r="K88">
         <v>94</v>
       </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M88">
+        <f t="shared" si="1"/>
+        <v>0.29424700140953064</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -3556,8 +3928,12 @@
       <c r="K89">
         <v>71</v>
       </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M89">
+        <f t="shared" si="1"/>
+        <v>0.28255019783973689</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -3591,8 +3967,12 @@
       <c r="K90">
         <v>24</v>
       </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M90">
+        <f t="shared" si="1"/>
+        <v>0.30416101813316343</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -3626,8 +4006,12 @@
       <c r="K91">
         <v>87</v>
       </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M91">
+        <f t="shared" si="1"/>
+        <v>0.43028590083122253</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -3661,8 +4045,12 @@
       <c r="K92">
         <v>47</v>
       </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M92">
+        <f t="shared" si="1"/>
+        <v>0.28061784505844112</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -3696,8 +4084,12 @@
       <c r="K93">
         <v>98</v>
       </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M93">
+        <f>F93-D93</f>
+        <v>0.302027839422226</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -3731,8 +4123,12 @@
       <c r="K94">
         <v>59</v>
       </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M94">
+        <f t="shared" si="1"/>
+        <v>0.16273335218429563</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -3766,8 +4162,12 @@
       <c r="K95">
         <v>51</v>
       </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M95">
+        <f>F95-D95</f>
+        <v>0.37184327244758608</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -3801,8 +4201,12 @@
       <c r="K96">
         <v>70</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M96">
+        <f t="shared" si="1"/>
+        <v>0.33767113983631142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -3836,8 +4240,12 @@
       <c r="K97">
         <v>94</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M97">
+        <f t="shared" si="1"/>
+        <v>0.29088701009750367</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -3871,8 +4279,12 @@
       <c r="K98">
         <v>50</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M98">
+        <f t="shared" si="1"/>
+        <v>0.2969129234552384</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -3906,8 +4318,12 @@
       <c r="K99">
         <v>58</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M99">
+        <f t="shared" si="1"/>
+        <v>0.48859674558043481</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -3941,8 +4357,12 @@
       <c r="K100">
         <v>39</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M100">
+        <f t="shared" si="1"/>
+        <v>0.27727368474006653</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -3976,9 +4396,13 @@
       <c r="K101">
         <v>41</v>
       </c>
+      <c r="M101">
+        <f t="shared" si="1"/>
+        <v>0.28971830606460569</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K1:K103 K105:K1048576">
+  <conditionalFormatting sqref="K1:K102 K105:K1048576 M1">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>70</formula>
     </cfRule>
